--- a/ASG/output/cube_analysis/s5378_cube_analysis_n2214gat_n2219gat_B_sa0.xlsx
+++ b/ASG/output/cube_analysis/s5378_cube_analysis_n2214gat_n2219gat_B_sa0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\koizumi\SAF_RPR_GEN\ASG\output\cube_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46E66A0E-0B79-4797-BFA3-9A8E4479C8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50A3BC2-69CB-49C8-96C5-AC6238F407D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{1E4691D7-010C-4DEB-BB9B-6FBA17235099}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{1E4691D7-010C-4DEB-BB9B-6FBA17235099}"/>
   </bookViews>
   <sheets>
     <sheet name="s5378_cube_analysis" sheetId="1" r:id="rId1"/>
@@ -30982,7 +30982,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -31640,15 +31640,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>523874</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:colOff>666751</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>176213</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>590549</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
